--- a/entregables/SIGRO - Tarjetas del Sprint 1 (todas).xlsx
+++ b/entregables/SIGRO - Tarjetas del Sprint 1 (todas).xlsx
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E529" s="15" t="inlineStr">
         <is>
-          <t>2 pts</t>
+          <t>3 pts</t>
         </is>
       </c>
       <c r="G529" s="13" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="J529" s="15" t="inlineStr">
         <is>
-          <t>2 pts</t>
+          <t>3 pts</t>
         </is>
       </c>
       <c r="L529" s="13" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="O529" s="15" t="inlineStr">
         <is>
-          <t>2 pts</t>
+          <t>3 pts</t>
         </is>
       </c>
     </row>
